--- a/public/fun/pack/xlsx/allowance/용돈기입장_45_대학생·청년_한지등불.xlsx
+++ b/public/fun/pack/xlsx/allowance/용돈기입장_45_대학생·청년_한지등불.xlsx
@@ -28,7 +28,7 @@
     <t>대학생·청년 용돈기입장</t>
   </si>
   <si>
-    <t>“한지 등불 아래 쓰는 소원 목록”</t>
+    <t>“친구 생일 선물 값 기록”</t>
   </si>
   <si>
     <t>한지 등불 테마</t>

--- a/public/fun/pack/xlsx/allowance/용돈기입장_45_대학생·청년_한지등불.xlsx
+++ b/public/fun/pack/xlsx/allowance/용돈기입장_45_대학생·청년_한지등불.xlsx
@@ -23,12 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="46">
   <si>
     <t>대학생·청년 용돈기입장</t>
-  </si>
-  <si>
-    <t>“친구 생일 선물 값 기록”</t>
   </si>
   <si>
     <t>한지 등불 테마</t>
@@ -1323,65 +1320,63 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="2:3" ht="6" customHeight="1"/>
     <row r="6" spans="2:3">
       <c r="B6" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="5"/>
     </row>
     <row r="7" spans="2:3" ht="22" customHeight="1">
       <c r="B7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>4</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="32" customHeight="1">
       <c r="B8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>6</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="32" customHeight="1">
       <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="22" customHeight="1">
       <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="28" customHeight="1">
       <c r="B12" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="8"/>
     </row>
     <row r="14" spans="2:3">
       <c r="B14" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="9"/>
     </row>
@@ -1424,21 +1419,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="12">
         <v>2026</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>1</v>
-      </c>
+      <c r="C2" s="13"/>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="14">
         <v>0</v>
@@ -1450,22 +1443,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="11" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1473,7 +1466,7 @@
         <v>46023</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="18">
@@ -1490,10 +1483,10 @@
         <v>46027</v>
       </c>
       <c r="B7" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>23</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>24</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="18">
@@ -1509,10 +1502,10 @@
         <v>46034</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18">
@@ -1528,10 +1521,10 @@
         <v>46041</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="18">
@@ -1547,7 +1540,7 @@
         <v>46054</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="18">
@@ -1564,10 +1557,10 @@
         <v>46058</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="18">
@@ -1583,10 +1576,10 @@
         <v>46065</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="18">
@@ -1602,10 +1595,10 @@
         <v>46072</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="18"/>
       <c r="E13" s="18">
@@ -1621,7 +1614,7 @@
         <v>46082</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="18">
@@ -1638,10 +1631,10 @@
         <v>46086</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18">
@@ -1657,10 +1650,10 @@
         <v>46093</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" s="18"/>
       <c r="E16" s="18">
@@ -1676,10 +1669,10 @@
         <v>46100</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" s="18"/>
       <c r="E17" s="18">
@@ -1695,7 +1688,7 @@
         <v>46113</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18">
@@ -1712,10 +1705,10 @@
         <v>46117</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="18"/>
       <c r="E19" s="18">
@@ -1731,10 +1724,10 @@
         <v>46124</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="18">
@@ -1750,10 +1743,10 @@
         <v>46131</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18">
@@ -1769,7 +1762,7 @@
         <v>46143</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="18">
@@ -1786,10 +1779,10 @@
         <v>46147</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="18">
@@ -1805,10 +1798,10 @@
         <v>46154</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="18">
@@ -1824,10 +1817,10 @@
         <v>46161</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" s="18"/>
       <c r="E25" s="18">
@@ -1843,7 +1836,7 @@
         <v>46174</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="18">
@@ -1860,10 +1853,10 @@
         <v>46178</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27" s="18"/>
       <c r="E27" s="18">
@@ -1879,10 +1872,10 @@
         <v>46185</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" s="18"/>
       <c r="E28" s="18">
@@ -1898,10 +1891,10 @@
         <v>46192</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D29" s="18"/>
       <c r="E29" s="18">
@@ -4992,7 +4985,7 @@
   <sheetData>
     <row r="1" spans="2:9">
       <c r="B1" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -5004,22 +4997,22 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>34</v>
-      </c>
       <c r="H4" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -5039,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H5)</f>
@@ -5063,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I6" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H6)</f>
@@ -5087,7 +5080,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H7)</f>
@@ -5111,7 +5104,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I8" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H8)</f>
@@ -5135,7 +5128,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I9" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H9)</f>
@@ -5159,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H10)</f>
@@ -5183,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I11" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H11)</f>
@@ -5207,7 +5200,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I12" s="18">
         <f>SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,H12)</f>
@@ -5231,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I13" s="25">
         <f>SUM(I5:I12)</f>
@@ -5291,7 +5284,7 @@
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" s="26">
         <f>SUM(C5:C16)</f>
@@ -5332,21 +5325,21 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1" s="20"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>38</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" s="14">
         <v>1800000</v>
@@ -5354,7 +5347,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" s="29">
         <f>StartBal+SUM('기입장'!$D$6:$D$305)-SUM('기입장'!$E$6:$E$305)+SUMIFS('기입장'!$E$6:$E$305,'기입장'!$C$6:$C$305,"저금")</f>
@@ -5363,7 +5356,7 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="30">
         <f>IF(C4=0,0,C6/C4)</f>
@@ -5372,7 +5365,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C8" s="29">
         <f>MAX(0,C4-C6)</f>
@@ -5381,7 +5374,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" s="29">
         <f>IFERROR(AVERAGEIF('월요약'!$E$5:$E$16,"&lt;&gt;0"),0)</f>
@@ -5390,7 +5383,7 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" s="31">
         <f>IF(C9&lt;=0,"-",IF(C8=0,"달성!",ROUNDUP(C8/C9,0)&amp;"개월"))</f>
@@ -5399,7 +5392,7 @@
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="8"/>
     </row>

--- a/public/fun/pack/xlsx/allowance/용돈기입장_45_대학생·청년_한지등불.xlsx
+++ b/public/fun/pack/xlsx/allowance/용돈기입장_45_대학생·청년_한지등불.xlsx
@@ -61,7 +61,7 @@
     <t>처음 들어 있는 줄은 예시예요. 지우고 내 용돈으로 바꿔 쓰세요.</t>
   </si>
   <si>
-    <t>우체국보험 상담 안내 · 자유롭게 고쳐 쓰세요</t>
+    <t>반딧불이의 곳간 · 자유롭게 고쳐 쓰세요</t>
   </si>
   <si>
     <t>기준 연도</t>
@@ -167,13 +167,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="#,##0"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="0&quot;월&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0;[Red]-#,##0"/>
-    <numFmt numFmtId="168" formatCode="0%"/>
-    <numFmt numFmtId="169" formatCode="@"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="&quot;올해&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="167" formatCode="0&quot;월&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0;[Red]-#,##0"/>
+    <numFmt numFmtId="169" formatCode="0%"/>
+    <numFmt numFmtId="170" formatCode="@"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -391,16 +392,16 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -409,19 +410,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -430,10 +431,10 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -442,13 +443,13 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
